--- a/Planning/BrickBuster-GanttChart.xlsx
+++ b/Planning/BrickBuster-GanttChart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arghi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7F7693-DE75-4D39-A34B-95F3300421BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{476A09F3-F1E6-4F11-BF27-921F60A851EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="67">
   <si>
     <t>Colours: Arghi = blue; Numan = green; Jack = purple; Ruth = amber; shared = grey; submission = red.</t>
   </si>
@@ -86,9 +86,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>Not recorded</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -233,10 +230,10 @@
     <t>Done</t>
   </si>
   <si>
-    <t>In progress</t>
-  </si>
-  <si>
     <t>Brick Buster Gantt Chart</t>
+  </si>
+  <si>
+    <t>Not started</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1027,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" s="46"/>
       <c r="F3" s="46"/>
@@ -1274,7 +1271,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J7" s="20"/>
       <c r="K7" s="21">
@@ -1374,10 +1371,10 @@
     </row>
     <row r="8" spans="1:35" ht="38" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>19</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>14</v>
@@ -1396,10 +1393,10 @@
         <v>2</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="21">
@@ -1496,16 +1493,16 @@
     </row>
     <row r="9" spans="1:35" ht="38" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="E9" s="5">
         <v>46293</v>
@@ -1518,10 +1515,10 @@
         <v>4</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="21">
@@ -1615,10 +1612,10 @@
     </row>
     <row r="10" spans="1:35" ht="38" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>14</v>
@@ -1637,10 +1634,10 @@
         <v>4</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="21">
@@ -1734,13 +1731,13 @@
     </row>
     <row r="11" spans="1:35" ht="38" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>15</v>
@@ -1756,10 +1753,10 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="21">
@@ -1853,16 +1850,16 @@
     </row>
     <row r="12" spans="1:35" ht="38" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="C12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="E12" s="5">
         <v>46297</v>
@@ -1875,10 +1872,10 @@
         <v>5</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="21">
@@ -1969,16 +1966,16 @@
     </row>
     <row r="13" spans="1:35" ht="38" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="5">
         <v>46297</v>
@@ -1991,10 +1988,10 @@
         <v>5</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="21">
@@ -2085,13 +2082,13 @@
     </row>
     <row r="14" spans="1:35" ht="38" customHeight="1">
       <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>41</v>
-      </c>
       <c r="C14" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>14</v>
@@ -2107,10 +2104,10 @@
         <v>5</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="21">
@@ -2198,10 +2195,10 @@
     </row>
     <row r="15" spans="1:35" ht="38" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -2220,10 +2217,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="21">
@@ -2326,16 +2323,16 @@
     </row>
     <row r="16" spans="1:35" ht="38" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="C16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="E16" s="5">
         <v>46302</v>
@@ -2348,10 +2345,10 @@
         <v>5</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="21">
@@ -2442,16 +2439,16 @@
     </row>
     <row r="17" spans="1:35" ht="38" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>50</v>
-      </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="5">
         <v>46302</v>
@@ -2464,10 +2461,10 @@
         <v>5</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="21">
@@ -2558,13 +2555,13 @@
     </row>
     <row r="18" spans="1:35" ht="38" customHeight="1">
       <c r="A18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>15</v>
@@ -2580,10 +2577,10 @@
         <v>3</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="21">
@@ -2680,10 +2677,10 @@
     </row>
     <row r="19" spans="1:35" ht="38" customHeight="1">
       <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>55</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>56</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>15</v>
@@ -2702,10 +2699,10 @@
         <v>2</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="21">
@@ -2805,10 +2802,10 @@
     </row>
     <row r="20" spans="1:35" ht="38" customHeight="1">
       <c r="A20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>14</v>
@@ -2827,10 +2824,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="21">
@@ -2933,16 +2930,16 @@
     </row>
     <row r="21" spans="1:35" ht="38" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>61</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" s="5">
         <v>46311</v>
@@ -2955,10 +2952,10 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="21">

--- a/Planning/BrickBuster-GanttChart.xlsx
+++ b/Planning/BrickBuster-GanttChart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arghi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katakuri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{476A09F3-F1E6-4F11-BF27-921F60A851EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BC58AC-D4C9-4F8D-837F-E28813936CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Gantt" sheetId="1" r:id="rId1"/>
@@ -233,7 +233,7 @@
     <t>Brick Buster Gantt Chart</t>
   </si>
   <si>
-    <t>Not started</t>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -561,6 +561,72 @@
     <xf numFmtId="166" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -571,72 +637,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -668,6 +668,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF526575"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF8B5EB5"/>
         </patternFill>
       </fill>
@@ -676,13 +683,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFD58B27"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF526575"/>
         </patternFill>
       </fill>
     </dxf>
@@ -937,7 +937,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI30"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30.25" customWidth="1"/>
@@ -988,7 +988,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35" ht="28.05" customHeight="1">
+    <row r="2" spans="1:35" ht="28.15" customHeight="1">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -1022,15 +1022,15 @@
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
-    <row r="3" spans="1:35" ht="23" customHeight="1">
+    <row r="3" spans="1:35" ht="23.1" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1061,7 +1061,7 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
     </row>
-    <row r="4" spans="1:35" ht="23" customHeight="1">
+    <row r="4" spans="1:35" ht="23.1" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1098,14 +1098,14 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
-    <row r="5" spans="1:35" ht="23" customHeight="1">
-      <c r="A5" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
+    <row r="5" spans="1:35" ht="23.1" customHeight="1">
+      <c r="A5" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1142,109 +1142,109 @@
       <c r="AI5" s="1"/>
     </row>
     <row r="6" spans="1:35" ht="30" customHeight="1">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="45">
+      <c r="J6" s="23"/>
+      <c r="K6" s="26">
         <v>46288</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="26">
         <v>46289</v>
       </c>
-      <c r="M6" s="45">
+      <c r="M6" s="26">
         <v>46290</v>
       </c>
-      <c r="N6" s="45">
+      <c r="N6" s="26">
         <v>46291</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="26">
         <v>46292</v>
       </c>
-      <c r="P6" s="45">
+      <c r="P6" s="26">
         <v>46293</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="26">
         <v>46294</v>
       </c>
-      <c r="R6" s="45">
+      <c r="R6" s="26">
         <v>46295</v>
       </c>
-      <c r="S6" s="45">
+      <c r="S6" s="26">
         <v>46296</v>
       </c>
-      <c r="T6" s="45">
+      <c r="T6" s="26">
         <v>46297</v>
       </c>
-      <c r="U6" s="45">
+      <c r="U6" s="26">
         <v>46298</v>
       </c>
-      <c r="V6" s="45">
+      <c r="V6" s="26">
         <v>46299</v>
       </c>
-      <c r="W6" s="45">
+      <c r="W6" s="26">
         <v>46300</v>
       </c>
-      <c r="X6" s="45">
+      <c r="X6" s="26">
         <v>46301</v>
       </c>
-      <c r="Y6" s="45">
+      <c r="Y6" s="26">
         <v>46302</v>
       </c>
-      <c r="Z6" s="45">
+      <c r="Z6" s="26">
         <v>46303</v>
       </c>
-      <c r="AA6" s="45">
+      <c r="AA6" s="26">
         <v>46304</v>
       </c>
-      <c r="AB6" s="45">
+      <c r="AB6" s="26">
         <v>46305</v>
       </c>
-      <c r="AC6" s="45">
+      <c r="AC6" s="26">
         <v>46306</v>
       </c>
-      <c r="AD6" s="45">
+      <c r="AD6" s="26">
         <v>46307</v>
       </c>
-      <c r="AE6" s="45">
+      <c r="AE6" s="26">
         <v>46308</v>
       </c>
-      <c r="AF6" s="45">
+      <c r="AF6" s="26">
         <v>46309</v>
       </c>
-      <c r="AG6" s="45">
+      <c r="AG6" s="26">
         <v>46310</v>
       </c>
-      <c r="AH6" s="45">
+      <c r="AH6" s="26">
         <v>46311</v>
       </c>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" ht="38" customHeight="1">
+    <row r="7" spans="1:35" ht="38.1" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1290,11 +1290,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="45">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P7" s="24"/>
+      <c r="P7" s="46"/>
       <c r="Q7" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="38" customHeight="1">
+    <row r="8" spans="1:35" ht="38.1" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
@@ -1415,8 +1415,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="26"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="48"/>
       <c r="Q8" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="38" customHeight="1">
+    <row r="9" spans="1:35" ht="38.1" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>24</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="21">
@@ -1541,13 +1541,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P9" s="27">
+      <c r="P9" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="29"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="32"/>
       <c r="T9" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="38" customHeight="1">
+    <row r="10" spans="1:35" ht="38.1" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>27</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="21">
@@ -1664,13 +1664,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="27">
+      <c r="Q10" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="29"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="32"/>
       <c r="U10" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="38" customHeight="1">
+    <row r="11" spans="1:35" ht="38.1" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>31</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="21">
@@ -1783,13 +1783,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="27">
+      <c r="Q11" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="29"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="32"/>
       <c r="U11" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AI11" s="1"/>
     </row>
-    <row r="12" spans="1:35" ht="38" customHeight="1">
+    <row r="12" spans="1:35" ht="38.1" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>34</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="21">
@@ -1914,14 +1914,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T12" s="27">
+      <c r="T12" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="29"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="32"/>
       <c r="Y12" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="38" customHeight="1">
+    <row r="13" spans="1:35" ht="38.1" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>38</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="21">
@@ -2030,14 +2030,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T13" s="30">
+      <c r="T13" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="32"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="34"/>
+      <c r="X13" s="35"/>
       <c r="Y13" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI13" s="1"/>
     </row>
-    <row r="14" spans="1:35" ht="38" customHeight="1">
+    <row r="14" spans="1:35" ht="38.1" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>39</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>38</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="21">
@@ -2146,11 +2146,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T14" s="33"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="X14" s="35"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="38"/>
       <c r="Y14" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AI14" s="1"/>
     </row>
-    <row r="15" spans="1:35" ht="38" customHeight="1">
+    <row r="15" spans="1:35" ht="38.1" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>43</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="21">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35" ht="38" customHeight="1">
+    <row r="16" spans="1:35" ht="38.1" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
@@ -2407,14 +2407,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="27">
+      <c r="Y16" s="30">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="28"/>
-      <c r="AC16" s="29"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="32"/>
       <c r="AD16" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="1:35" ht="38" customHeight="1">
+    <row r="17" spans="1:35" ht="38.1" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
@@ -2523,14 +2523,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="27">
+      <c r="Y17" s="30">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="28"/>
-      <c r="AC17" s="29"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="32"/>
       <c r="AD17" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AI17" s="1"/>
     </row>
-    <row r="18" spans="1:35" ht="38" customHeight="1">
+    <row r="18" spans="1:35" ht="38.1" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>50</v>
       </c>
@@ -2655,12 +2655,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC18" s="36">
+      <c r="AC18" s="39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AD18" s="37"/>
-      <c r="AE18" s="38"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="41"/>
       <c r="AF18" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AI18" s="1"/>
     </row>
-    <row r="19" spans="1:35" ht="38" customHeight="1">
+    <row r="19" spans="1:35" ht="38.1" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
@@ -2785,11 +2785,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="27">
+      <c r="AE19" s="30">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AF19" s="29"/>
+      <c r="AF19" s="32"/>
       <c r="AG19" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AI19" s="1"/>
     </row>
-    <row r="20" spans="1:35" ht="38" customHeight="1">
+    <row r="20" spans="1:35" ht="38.1" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>57</v>
       </c>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="AI20" s="1"/>
     </row>
-    <row r="21" spans="1:35" ht="38" customHeight="1">
+    <row r="21" spans="1:35" ht="38.1" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
@@ -3391,11 +3391,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="T13:X14"/>
-    <mergeCell ref="Y16:AC16"/>
     <mergeCell ref="Y17:AC17"/>
     <mergeCell ref="AC18:AE18"/>
     <mergeCell ref="AE19:AF19"/>
@@ -3405,8 +3400,13 @@
     <mergeCell ref="P9:S9"/>
     <mergeCell ref="Q10:T10"/>
     <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="T13:X14"/>
+    <mergeCell ref="Y16:AC16"/>
   </mergeCells>
-  <conditionalFormatting sqref="K8:N8 K7:O7 Q7:AH8">
+  <conditionalFormatting sqref="K7:O7 Q7:AH8 K8:N8">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
@@ -3431,28 +3431,28 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K14:S14 K13:T13 Y13:AH14">
+  <conditionalFormatting sqref="K13:T13 Y13:AH14 K14:S14">
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K15:AH15">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K16:Y16 AD16:AH16">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17:Y17 AD17:AH17">
-    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19:AE19 K18:AC18 AF18:AH18 AG19:AH19">
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+  <conditionalFormatting sqref="K18:AC18 AF18:AH18 K19:AE19 AG19:AH19">
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K15:AH15">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Planning/BrickBuster-GanttChart.xlsx
+++ b/Planning/BrickBuster-GanttChart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katakuri\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arghi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BC58AC-D4C9-4F8D-837F-E28813936CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE6D571-DF67-45F0-8F4D-4A2A681C5364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Gantt" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="69">
   <si>
     <t>Colours: Arghi = blue; Numan = green; Jack = purple; Ruth = amber; shared = grey; submission = red.</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>Brick Buster Gantt Chart</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>In review</t>
   </si>
   <si>
     <t>In progress</t>
@@ -937,7 +943,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI30"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30.25" customWidth="1"/>
@@ -988,7 +994,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35" ht="28.15" customHeight="1">
+    <row r="2" spans="1:35" ht="28.05" customHeight="1">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -1022,7 +1028,7 @@
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
-    <row r="3" spans="1:35" ht="23.1" customHeight="1">
+    <row r="3" spans="1:35" ht="23" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1061,7 +1067,7 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
     </row>
-    <row r="4" spans="1:35" ht="23.1" customHeight="1">
+    <row r="4" spans="1:35" ht="23" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1098,7 +1104,7 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
-    <row r="5" spans="1:35" ht="23.1" customHeight="1">
+    <row r="5" spans="1:35" ht="23" customHeight="1">
       <c r="A5" s="29" t="s">
         <v>0</v>
       </c>
@@ -1244,7 +1250,7 @@
       </c>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" ht="38.1" customHeight="1">
+    <row r="7" spans="1:35" ht="38" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1369,7 +1375,7 @@
       </c>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="38.1" customHeight="1">
+    <row r="8" spans="1:35" ht="38" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
@@ -1491,7 +1497,7 @@
       </c>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="38.1" customHeight="1">
+    <row r="9" spans="1:35" ht="38" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1610,7 +1616,7 @@
       </c>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="38.1" customHeight="1">
+    <row r="10" spans="1:35" ht="38" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -1729,7 +1735,7 @@
       </c>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="38.1" customHeight="1">
+    <row r="11" spans="1:35" ht="38" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -1848,7 +1854,7 @@
       </c>
       <c r="AI11" s="1"/>
     </row>
-    <row r="12" spans="1:35" ht="38.1" customHeight="1">
+    <row r="12" spans="1:35" ht="38" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
@@ -1964,7 +1970,7 @@
       </c>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="38.1" customHeight="1">
+    <row r="13" spans="1:35" ht="38" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
@@ -2080,7 +2086,7 @@
       </c>
       <c r="AI13" s="1"/>
     </row>
-    <row r="14" spans="1:35" ht="38.1" customHeight="1">
+    <row r="14" spans="1:35" ht="38" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>39</v>
       </c>
@@ -2193,7 +2199,7 @@
       </c>
       <c r="AI14" s="1"/>
     </row>
-    <row r="15" spans="1:35" ht="38.1" customHeight="1">
+    <row r="15" spans="1:35" ht="38" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -2220,7 +2226,7 @@
         <v>43</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="21">
@@ -2321,7 +2327,7 @@
       </c>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35" ht="38.1" customHeight="1">
+    <row r="16" spans="1:35" ht="38" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
@@ -2348,7 +2354,7 @@
         <v>47</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="21">
@@ -2437,7 +2443,7 @@
       </c>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="1:35" ht="38.1" customHeight="1">
+    <row r="17" spans="1:35" ht="38" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
@@ -2464,7 +2470,7 @@
         <v>47</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="21">
@@ -2553,7 +2559,7 @@
       </c>
       <c r="AI17" s="1"/>
     </row>
-    <row r="18" spans="1:35" ht="38.1" customHeight="1">
+    <row r="18" spans="1:35" ht="38" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>50</v>
       </c>
@@ -2580,7 +2586,7 @@
         <v>53</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="21">
@@ -2675,7 +2681,7 @@
       </c>
       <c r="AI18" s="1"/>
     </row>
-    <row r="19" spans="1:35" ht="38.1" customHeight="1">
+    <row r="19" spans="1:35" ht="38" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
@@ -2702,7 +2708,7 @@
         <v>56</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="21">
@@ -2800,7 +2806,7 @@
       </c>
       <c r="AI19" s="1"/>
     </row>
-    <row r="20" spans="1:35" ht="38.1" customHeight="1">
+    <row r="20" spans="1:35" ht="38" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>57</v>
       </c>
@@ -2827,7 +2833,7 @@
         <v>59</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="21">
@@ -2928,7 +2934,7 @@
       </c>
       <c r="AI20" s="1"/>
     </row>
-    <row r="21" spans="1:35" ht="38.1" customHeight="1">
+    <row r="21" spans="1:35" ht="38" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
